--- a/image processing/chapter3.xlsx
+++ b/image processing/chapter3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D 資料匣\課程\勤益課程\數位影像\PPT\授課版_(教師專用)\excel\chapter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D 資料匣\課程\勤益課程\數位影像\image processing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78BB3D8-683C-4BFA-83B8-9D35B59188B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69327598-44F7-406A-AAF3-D063FC6DA866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29320" yWindow="3640" windowWidth="28800" windowHeight="15320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-36200" yWindow="-3880" windowWidth="28800" windowHeight="15320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="240">
   <si>
     <t>question</t>
   </si>
@@ -38,507 +38,6 @@
   </si>
   <si>
     <t>answer</t>
-  </si>
-  <si>
-    <t>在Matlab中，讀取影像的函數是？</t>
-  </si>
-  <si>
-    <t>imload</t>
-  </si>
-  <si>
-    <t>readimage</t>
-  </si>
-  <si>
-    <t>loadimg</t>
-  </si>
-  <si>
-    <t>imread</t>
-  </si>
-  <si>
-    <t>在Matlab中，顯示影像的函數是？</t>
-  </si>
-  <si>
-    <t>viewimage</t>
-  </si>
-  <si>
-    <t>display</t>
-  </si>
-  <si>
-    <t>imshow</t>
-  </si>
-  <si>
-    <t>showimg</t>
-  </si>
-  <si>
-    <t>在Matlab中，儲存影像的函數是？</t>
-  </si>
-  <si>
-    <t>imsave</t>
-  </si>
-  <si>
-    <t>writeimg</t>
-  </si>
-  <si>
-    <t>imwrite</t>
-  </si>
-  <si>
-    <t>saveimage</t>
-  </si>
-  <si>
-    <t>Matlab中，size函數用於？</t>
-  </si>
-  <si>
-    <t>改變影像大小</t>
-  </si>
-  <si>
-    <t>取得影像尺寸</t>
-  </si>
-  <si>
-    <t>壓縮影像</t>
-  </si>
-  <si>
-    <t>旋轉影像</t>
-  </si>
-  <si>
-    <t>在Matlab中，rgb2gray函數的功能是？</t>
-  </si>
-  <si>
-    <t>反轉顏色</t>
-  </si>
-  <si>
-    <t>調整亮度</t>
-  </si>
-  <si>
-    <t>彩色轉灰階</t>
-  </si>
-  <si>
-    <t>灰階轉彩色</t>
-  </si>
-  <si>
-    <t>Matlab中，im2double函數的作用是？</t>
-  </si>
-  <si>
-    <t>複製影像</t>
-  </si>
-  <si>
-    <t>影像加倍</t>
-  </si>
-  <si>
-    <t>雙倍解析度</t>
-  </si>
-  <si>
-    <t>轉換為雙精度浮點數</t>
-  </si>
-  <si>
-    <t>在Matlab中，imresize函數用於？</t>
-  </si>
-  <si>
-    <t>翻轉影像</t>
-  </si>
-  <si>
-    <t>縮放影像</t>
-  </si>
-  <si>
-    <t>裁切影像</t>
-  </si>
-  <si>
-    <t>Matlab中，imrotate函數的功能是？</t>
-  </si>
-  <si>
-    <t>縮放</t>
-  </si>
-  <si>
-    <t>旋轉</t>
-  </si>
-  <si>
-    <t>平移</t>
-  </si>
-  <si>
-    <t>翻轉</t>
-  </si>
-  <si>
-    <t>在Matlab中，imhist函數用於？</t>
-  </si>
-  <si>
-    <t>儲存影像</t>
-  </si>
-  <si>
-    <t>計算直方圖</t>
-  </si>
-  <si>
-    <t>顯示影像</t>
-  </si>
-  <si>
-    <t>Matlab中，histeq函數的功能是？</t>
-  </si>
-  <si>
-    <t>直方圖刪除</t>
-  </si>
-  <si>
-    <t>直方圖儲存</t>
-  </si>
-  <si>
-    <t>直方圖均化</t>
-  </si>
-  <si>
-    <t>直方圖顯示</t>
-  </si>
-  <si>
-    <t>在Matlab中，imadjust函數用於？</t>
-  </si>
-  <si>
-    <t>改變大小</t>
-  </si>
-  <si>
-    <t>調整對比度</t>
-  </si>
-  <si>
-    <t>Matlab中，imcomplement函數的作用是？</t>
-  </si>
-  <si>
-    <t>增強對比</t>
-  </si>
-  <si>
-    <t>去除雜訊</t>
-  </si>
-  <si>
-    <t>產生負片</t>
-  </si>
-  <si>
-    <t>在Matlab中，fspecial函數用於？</t>
-  </si>
-  <si>
-    <t>建立濾波器</t>
-  </si>
-  <si>
-    <t>讀取影像</t>
-  </si>
-  <si>
-    <t>Matlab中，imfilter函數的功能是？</t>
-  </si>
-  <si>
-    <t>格式轉換</t>
-  </si>
-  <si>
-    <t>濾波處理</t>
-  </si>
-  <si>
-    <t>在Matlab中，medfilt2函數用於？</t>
-  </si>
-  <si>
-    <t>拉普拉斯濾波</t>
-  </si>
-  <si>
-    <t>平均濾波</t>
-  </si>
-  <si>
-    <t>中值濾波</t>
-  </si>
-  <si>
-    <t>高斯濾波</t>
-  </si>
-  <si>
-    <t>Matlab中，edge函數的功能是？</t>
-  </si>
-  <si>
-    <t>影像分割</t>
-  </si>
-  <si>
-    <t>色彩轉換</t>
-  </si>
-  <si>
-    <t>邊緣檢測</t>
-  </si>
-  <si>
-    <t>平滑影像</t>
-  </si>
-  <si>
-    <t>在Matlab中，im2bw函數用於？</t>
-  </si>
-  <si>
-    <t>灰階轉二值</t>
-  </si>
-  <si>
-    <t>彩色轉二值</t>
-  </si>
-  <si>
-    <t>二值轉灰階</t>
-  </si>
-  <si>
-    <t>Matlab中，graythresh函數的作用是？</t>
-  </si>
-  <si>
-    <t>手動設定閾值</t>
-  </si>
-  <si>
-    <t>自動計算閾值</t>
-  </si>
-  <si>
-    <t>增強亮度</t>
-  </si>
-  <si>
-    <t>在Matlab中，imdilate函數用於？</t>
-  </si>
-  <si>
-    <t>開運算</t>
-  </si>
-  <si>
-    <t>閉運算</t>
-  </si>
-  <si>
-    <t>膨脹</t>
-  </si>
-  <si>
-    <t>侵蝕</t>
-  </si>
-  <si>
-    <t>Matlab中，imerode函數的功能是？</t>
-  </si>
-  <si>
-    <t>在Matlab中，imopen函數用於？</t>
-  </si>
-  <si>
-    <t>Matlab中，imclose函數的功能是？</t>
-  </si>
-  <si>
-    <t>在Matlab中，strel函數用於？</t>
-  </si>
-  <si>
-    <t>建立結構元素</t>
-  </si>
-  <si>
-    <t>Matlab中，bwlabel函數的作用是？</t>
-  </si>
-  <si>
-    <t>雜訊標記</t>
-  </si>
-  <si>
-    <t>邊緣標記</t>
-  </si>
-  <si>
-    <t>色彩標記</t>
-  </si>
-  <si>
-    <t>連通區域標記</t>
-  </si>
-  <si>
-    <t>在Matlab中，regionprops函數用於？</t>
-  </si>
-  <si>
-    <t>區域特徵提取</t>
-  </si>
-  <si>
-    <t>Matlab中，imcrop函數的功能是？</t>
-  </si>
-  <si>
-    <t>裁切</t>
-  </si>
-  <si>
-    <t>在Matlab中，imtranslate函數用於？</t>
-  </si>
-  <si>
-    <t>Matlab中，fliplr函數的作用是？</t>
-  </si>
-  <si>
-    <t>旋轉180度</t>
-  </si>
-  <si>
-    <t>旋轉90度</t>
-  </si>
-  <si>
-    <t>左右翻轉</t>
-  </si>
-  <si>
-    <t>上下翻轉</t>
-  </si>
-  <si>
-    <t>在Matlab中，flipud函數用於？</t>
-  </si>
-  <si>
-    <t>Matlab中，fft2函數的功能是？</t>
-  </si>
-  <si>
-    <t>一維傅立葉轉換</t>
-  </si>
-  <si>
-    <t>反傅立葉轉換</t>
-  </si>
-  <si>
-    <t>離散餘弦轉換</t>
-  </si>
-  <si>
-    <t>二維傅立葉轉換</t>
-  </si>
-  <si>
-    <t>在Matlab中，ifft2函數用於？</t>
-  </si>
-  <si>
-    <t>傅立葉轉換</t>
-  </si>
-  <si>
-    <t>小波轉換</t>
-  </si>
-  <si>
-    <t>Matlab中，fftshift函數的作用是？</t>
-  </si>
-  <si>
-    <t>移動零頻到中心</t>
-  </si>
-  <si>
-    <t>反FFT</t>
-  </si>
-  <si>
-    <t>計算FFT</t>
-  </si>
-  <si>
-    <t>濾波</t>
-  </si>
-  <si>
-    <t>在Matlab中，imabsdiff函數用於？</t>
-  </si>
-  <si>
-    <t>影像相乘</t>
-  </si>
-  <si>
-    <t>影像相減</t>
-  </si>
-  <si>
-    <t>影像相加</t>
-  </si>
-  <si>
-    <t>影像絕對差</t>
-  </si>
-  <si>
-    <t>Matlab中，imadd函數的功能是？</t>
-  </si>
-  <si>
-    <t>影像相除</t>
-  </si>
-  <si>
-    <t>在Matlab中，imsubtract函數用於？</t>
-  </si>
-  <si>
-    <t>Matlab中，immultiply函數的作用是？</t>
-  </si>
-  <si>
-    <t>在Matlab中，imdivide函數用於？</t>
-  </si>
-  <si>
-    <t>Matlab中，wiener2函數的功能是？</t>
-  </si>
-  <si>
-    <t>維納濾波</t>
-  </si>
-  <si>
-    <t>在Matlab中，imnoise函數用於？</t>
-  </si>
-  <si>
-    <t>分析雜訊</t>
-  </si>
-  <si>
-    <t>加入雜訊</t>
-  </si>
-  <si>
-    <t>檢測雜訊</t>
-  </si>
-  <si>
-    <t>Matlab中，bwareaopen函數的作用是？</t>
-  </si>
-  <si>
-    <t>移除小物件</t>
-  </si>
-  <si>
-    <t>在Matlab中，bwmorph函數用於？</t>
-  </si>
-  <si>
-    <t>形態學操作</t>
-  </si>
-  <si>
-    <t>Matlab中，imfill函數的功能是？</t>
-  </si>
-  <si>
-    <t>去除物件</t>
-  </si>
-  <si>
-    <t>填充孔洞</t>
-  </si>
-  <si>
-    <t>在Matlab中，bwperim函數用於？</t>
-  </si>
-  <si>
-    <t>填充</t>
-  </si>
-  <si>
-    <t>尋找邊界</t>
-  </si>
-  <si>
-    <t>Matlab中，imcontour函數的作用是？</t>
-  </si>
-  <si>
-    <t>分割</t>
-  </si>
-  <si>
-    <t>顯示等高線</t>
-  </si>
-  <si>
-    <t>在Matlab中，impixel函數用於？</t>
-  </si>
-  <si>
-    <t>取得像素值</t>
-  </si>
-  <si>
-    <t>刪除像素</t>
-  </si>
-  <si>
-    <t>設定像素值</t>
-  </si>
-  <si>
-    <t>計算像素數</t>
-  </si>
-  <si>
-    <t>Matlab中，imtool函數的功能是？</t>
-  </si>
-  <si>
-    <t>開啟影像工具</t>
-  </si>
-  <si>
-    <t>在Matlab中，montage函數用於？</t>
-  </si>
-  <si>
-    <t>顯示單張影像</t>
-  </si>
-  <si>
-    <t>顯示多張影像</t>
-  </si>
-  <si>
-    <t>Matlab中，imfinfo函數的作用是？</t>
-  </si>
-  <si>
-    <t>取得影像資訊</t>
-  </si>
-  <si>
-    <t>在Matlab中，uint8函數用於？</t>
-  </si>
-  <si>
-    <t>轉換為8位元整數</t>
-  </si>
-  <si>
-    <t>轉換為雙精度</t>
-  </si>
-  <si>
-    <t>轉換為16位元整數</t>
-  </si>
-  <si>
-    <t>轉換為浮點數</t>
-  </si>
-  <si>
-    <t>Matlab中，double函數的功能是？</t>
-  </si>
-  <si>
-    <t>雙倍大小</t>
-  </si>
-  <si>
-    <t>轉換為整數</t>
   </si>
   <si>
     <t>title</t>
@@ -551,7 +50,697 @@
     <t>chapter_name</t>
   </si>
   <si>
-    <t>CH 03 影像之Matlab</t>
+    <t>飽和度</t>
+  </si>
+  <si>
+    <t>色調</t>
+  </si>
+  <si>
+    <t>對比度</t>
+  </si>
+  <si>
+    <t>相容性最好</t>
+  </si>
+  <si>
+    <t>僅有像素資料</t>
+  </si>
+  <si>
+    <t>減少雜訊</t>
+  </si>
+  <si>
+    <t>旋轉影像</t>
+  </si>
+  <si>
+    <t>影像處理程式操作中,下列哪兩個是最基礎的操作?</t>
+  </si>
+  <si>
+    <t>讀取與顯示</t>
+  </si>
+  <si>
+    <t>壓縮與解壓縮</t>
+  </si>
+  <si>
+    <t>編輯與儲存</t>
+  </si>
+  <si>
+    <t>轉換與濾波</t>
+  </si>
+  <si>
+    <t>OpenCV中用來表示影像的主要類別是?</t>
+  </si>
+  <si>
+    <t>Image</t>
+  </si>
+  <si>
+    <t>Mat</t>
+  </si>
+  <si>
+    <t>Picture</t>
+  </si>
+  <si>
+    <t>Array</t>
+  </si>
+  <si>
+    <t>Mat類別在OpenCV中主要負責儲存什麼?</t>
+  </si>
+  <si>
+    <t>音訊資料</t>
+  </si>
+  <si>
+    <t>文字資料</t>
+  </si>
+  <si>
+    <t>影像的像素資訊</t>
+  </si>
+  <si>
+    <t>網路封包</t>
+  </si>
+  <si>
+    <t>OpenCV中負責色彩空間轉換的核心函數名稱為?</t>
+  </si>
+  <si>
+    <t>convertColor</t>
+  </si>
+  <si>
+    <t>changeColor</t>
+  </si>
+  <si>
+    <t>transformColor</t>
+  </si>
+  <si>
+    <t>cvtColor</t>
+  </si>
+  <si>
+    <t>cvtColor函數的第一個參數應該放入什麼?</t>
+  </si>
+  <si>
+    <t>輸入的Mat類別影像</t>
+  </si>
+  <si>
+    <t>輸出的影像</t>
+  </si>
+  <si>
+    <t>轉換類型</t>
+  </si>
+  <si>
+    <t>色彩空間代碼</t>
+  </si>
+  <si>
+    <t>在cvtColor函數中,第二個參數的作用是?</t>
+  </si>
+  <si>
+    <t>輸入影像</t>
+  </si>
+  <si>
+    <t>轉換後輸出的Mat類別影像</t>
+  </si>
+  <si>
+    <t>色彩深度</t>
+  </si>
+  <si>
+    <t>影像大小</t>
+  </si>
+  <si>
+    <t>cvtColor函數的第三個參數使用什麼類型來代表不同的顏色空間轉換?</t>
+  </si>
+  <si>
+    <t>字串</t>
+  </si>
+  <si>
+    <t>布林值</t>
+  </si>
+  <si>
+    <t>數字</t>
+  </si>
+  <si>
+    <t>陣列</t>
+  </si>
+  <si>
+    <t>關於二值影像在影像處理中的地位,下列何者正確?</t>
+  </si>
+  <si>
+    <t>罕見的資料類型</t>
+  </si>
+  <si>
+    <t>已淘汰的資料類型</t>
+  </si>
+  <si>
+    <t>實驗性的資料類型</t>
+  </si>
+  <si>
+    <t>很常見的資料類型</t>
+  </si>
+  <si>
+    <t>影像加法運算最直接的效果是?</t>
+  </si>
+  <si>
+    <t>增強亮度</t>
+  </si>
+  <si>
+    <t>銳化邊緣</t>
+  </si>
+  <si>
+    <t>壓縮檔案</t>
+  </si>
+  <si>
+    <t>利用加法運算合併兩個影像可以創建什麼效果?</t>
+  </si>
+  <si>
+    <t>模糊效果</t>
+  </si>
+  <si>
+    <t>重疊或混合效果</t>
+  </si>
+  <si>
+    <t>銳化效果</t>
+  </si>
+  <si>
+    <t>反轉效果</t>
+  </si>
+  <si>
+    <t>對影像進行減法運算會造成什麼結果?</t>
+  </si>
+  <si>
+    <t>使影像變亮</t>
+  </si>
+  <si>
+    <t>增加對比</t>
+  </si>
+  <si>
+    <t>使影像變暗</t>
+  </si>
+  <si>
+    <t>增加飽和度</t>
+  </si>
+  <si>
+    <t>影像減法常應用於哪些領域來找出兩畫格之間的差異?</t>
+  </si>
+  <si>
+    <t>色彩校正</t>
+  </si>
+  <si>
+    <t>影像壓縮</t>
+  </si>
+  <si>
+    <t>格式轉換</t>
+  </si>
+  <si>
+    <t>運動偵測或背景消除</t>
+  </si>
+  <si>
+    <t>影像乘法中,乘以小於1的數值會產生什麼效果?</t>
+  </si>
+  <si>
+    <t>降低像素強度</t>
+  </si>
+  <si>
+    <t>增加像素強度</t>
+  </si>
+  <si>
+    <t>不改變強度</t>
+  </si>
+  <si>
+    <t>反轉顏色</t>
+  </si>
+  <si>
+    <t>若要增加影像的像素強度,應該在乘法運算中使用什麼數值?</t>
+  </si>
+  <si>
+    <t>小於1的值</t>
+  </si>
+  <si>
+    <t>大於1的值</t>
+  </si>
+  <si>
+    <t>等於1的值</t>
+  </si>
+  <si>
+    <t>負值</t>
+  </si>
+  <si>
+    <t>影像除法運算在影像處理中主要用於什麼目的?</t>
+  </si>
+  <si>
+    <t>增加解析度</t>
+  </si>
+  <si>
+    <t>壓縮影像</t>
+  </si>
+  <si>
+    <t>進行正規化</t>
+  </si>
+  <si>
+    <t>影像的放大/縮小操作可以達成什麼目標?</t>
+  </si>
+  <si>
+    <t>改變色彩</t>
+  </si>
+  <si>
+    <t>去除雜訊</t>
+  </si>
+  <si>
+    <t>調整解析度</t>
+  </si>
+  <si>
+    <t>在Matlab中,讀取影像後會在編輯器的哪個區域顯示?</t>
+  </si>
+  <si>
+    <t>workspace</t>
+  </si>
+  <si>
+    <t>command window</t>
+  </si>
+  <si>
+    <t>current folder</t>
+  </si>
+  <si>
+    <t>editor</t>
+  </si>
+  <si>
+    <t>OpenCV的官方文件可以在哪個網址找到?</t>
+  </si>
+  <si>
+    <t>https://opencv.com/</t>
+  </si>
+  <si>
+    <t>https://docs.opencv.org/</t>
+  </si>
+  <si>
+    <t>https://www.opencv.net/</t>
+  </si>
+  <si>
+    <t>https://opencv.github.io/</t>
+  </si>
+  <si>
+    <t>影像動作(Image Operations)在數位影像處理中的定位為何?</t>
+  </si>
+  <si>
+    <t>進階技術</t>
+  </si>
+  <si>
+    <t>實驗性功能</t>
+  </si>
+  <si>
+    <t>基礎操作</t>
+  </si>
+  <si>
+    <t>選用功能</t>
+  </si>
+  <si>
+    <t>本章節主要介紹哪兩個影像處理工具的基礎實作?</t>
+  </si>
+  <si>
+    <t>Photoshop與GIMP</t>
+  </si>
+  <si>
+    <t>Python與Java</t>
+  </si>
+  <si>
+    <t>C#與JavaScript</t>
+  </si>
+  <si>
+    <t>Matlab與OpenCV</t>
+  </si>
+  <si>
+    <t>在C++中,Mat對象可以進行哪些類型的操作?</t>
+  </si>
+  <si>
+    <t>讀取、修改、儲存、計算等各種影像處理操作</t>
+  </si>
+  <si>
+    <t>僅能讀取</t>
+  </si>
+  <si>
+    <t>僅能顯示</t>
+  </si>
+  <si>
+    <t>僅能儲存</t>
+  </si>
+  <si>
+    <t>關於cvtColor函數的第四個參數,下列敘述何者正確?</t>
+  </si>
+  <si>
+    <t>必須輸入</t>
+  </si>
+  <si>
+    <t>可以不輸入</t>
+  </si>
+  <si>
+    <t>必須為0</t>
+  </si>
+  <si>
+    <t>必須為字串</t>
+  </si>
+  <si>
+    <t>Matlab中的色彩空間轉換函數通常以什麼形式提供給使用者?</t>
+  </si>
+  <si>
+    <t>圖表</t>
+  </si>
+  <si>
+    <t>流程圖</t>
+  </si>
+  <si>
+    <t>列表清單</t>
+  </si>
+  <si>
+    <t>樹狀圖</t>
+  </si>
+  <si>
+    <t>影像動作(Image Operations)的主要目的為何?</t>
+  </si>
+  <si>
+    <t>增加檔案大小</t>
+  </si>
+  <si>
+    <t>減少處理時間</t>
+  </si>
+  <si>
+    <t>簡化程式碼</t>
+  </si>
+  <si>
+    <t>對影像進行調整以滿足特定需求或得到所需效果</t>
+  </si>
+  <si>
+    <t>向影像加上一個固定的亮度值會產生什麼效果?</t>
+  </si>
+  <si>
+    <t>使整體影像變亮</t>
+  </si>
+  <si>
+    <t>使整體影像變暗</t>
+  </si>
+  <si>
+    <t>不改變亮度</t>
+  </si>
+  <si>
+    <t>影像乘法運算最常用於調整影像的哪個屬性?</t>
+  </si>
+  <si>
+    <t>解析度</t>
+  </si>
+  <si>
+    <t>在強度校正的應用中,影像除法主要用於什麼處理?</t>
+  </si>
+  <si>
+    <t>增加亮度</t>
+  </si>
+  <si>
+    <t>作者建議使用雙重for迴圈處理影像的第一個優點是什麼?</t>
+  </si>
+  <si>
+    <t>速度最快</t>
+  </si>
+  <si>
+    <t>記憶體使用最少</t>
+  </si>
+  <si>
+    <t>程式碼最短</t>
+  </si>
+  <si>
+    <t>更加直觀</t>
+  </si>
+  <si>
+    <t>使用雙重for迴圈的第二個優點是?</t>
+  </si>
+  <si>
+    <t>能寫得更底層,代表能有更多的變換</t>
+  </si>
+  <si>
+    <t>自動優化</t>
+  </si>
+  <si>
+    <t>不需要除錯</t>
+  </si>
+  <si>
+    <t>雙重for迴圈的第三個優點為何?</t>
+  </si>
+  <si>
+    <t>程式碼最簡潔</t>
+  </si>
+  <si>
+    <t>完成數學組合後可修改為向量法來加速處理</t>
+  </si>
+  <si>
+    <t>不需要學習</t>
+  </si>
+  <si>
+    <t>自動平行化</t>
+  </si>
+  <si>
+    <t>OpenCV支援的影像格式資訊在官方文件中如何呈現?</t>
+  </si>
+  <si>
+    <t>文字說明</t>
+  </si>
+  <si>
+    <t>程式碼範例</t>
+  </si>
+  <si>
+    <t>表格</t>
+  </si>
+  <si>
+    <t>影片教學</t>
+  </si>
+  <si>
+    <t>運動偵測應用中最常使用哪種影像運算?</t>
+  </si>
+  <si>
+    <t>加法</t>
+  </si>
+  <si>
+    <t>乘法</t>
+  </si>
+  <si>
+    <t>除法</t>
+  </si>
+  <si>
+    <t>減法</t>
+  </si>
+  <si>
+    <t>背景消除技術主要依賴哪種影像運算來找出差異?</t>
+  </si>
+  <si>
+    <t>若要降低影像的像素強度,應該採用哪種運算方式?</t>
+  </si>
+  <si>
+    <t>加上正值</t>
+  </si>
+  <si>
+    <t>乘以小於1的值</t>
+  </si>
+  <si>
+    <t>加上負值</t>
+  </si>
+  <si>
+    <t>除以小於1的值</t>
+  </si>
+  <si>
+    <t>使影像整體變亮最直接的方法是?</t>
+  </si>
+  <si>
+    <t>減去一個值</t>
+  </si>
+  <si>
+    <t>加上一個正值</t>
+  </si>
+  <si>
+    <t>除以大於1的值</t>
+  </si>
+  <si>
+    <t>要使影像整體變暗,可以使用下列哪種運算?</t>
+  </si>
+  <si>
+    <t>放大</t>
+  </si>
+  <si>
+    <t>色彩轉換</t>
+  </si>
+  <si>
+    <t>將影像縮放到所需的尺寸大小應該使用什麼操作?</t>
+  </si>
+  <si>
+    <t>放大/縮小</t>
+  </si>
+  <si>
+    <t>加減運算</t>
+  </si>
+  <si>
+    <t>乘除運算</t>
+  </si>
+  <si>
+    <t>Mat類別在OpenCV中的重要性如何?</t>
+  </si>
+  <si>
+    <t>較少使用的類別</t>
+  </si>
+  <si>
+    <t>最常用的類別之一</t>
+  </si>
+  <si>
+    <t>已棄用的類別</t>
+  </si>
+  <si>
+    <t>實驗性類別</t>
+  </si>
+  <si>
+    <t>本章介紹的OpenCV支援哪些程式語言?</t>
+  </si>
+  <si>
+    <t>僅C++</t>
+  </si>
+  <si>
+    <t>僅Python</t>
+  </si>
+  <si>
+    <t>C++和Python</t>
+  </si>
+  <si>
+    <t>僅Java</t>
+  </si>
+  <si>
+    <t>將雙重迴圈修改為向量法的主要好處是?</t>
+  </si>
+  <si>
+    <t>程式碼更長</t>
+  </si>
+  <si>
+    <t>更容易理解</t>
+  </si>
+  <si>
+    <t>減少記憶體使用</t>
+  </si>
+  <si>
+    <t>可以加速處理</t>
+  </si>
+  <si>
+    <t>要創建兩個影像的重疊效果,應該使用哪種運算,並且需要注意什麼?</t>
+  </si>
+  <si>
+    <t>加法,注意避免溢位</t>
+  </si>
+  <si>
+    <t>減法,注意避免負值</t>
+  </si>
+  <si>
+    <t>乘法,注意對比度</t>
+  </si>
+  <si>
+    <t>除法,注意除以零</t>
+  </si>
+  <si>
+    <t>當一個影像被另一個影像除以時進行正規化,這在什麼情況下特別有用?</t>
+  </si>
+  <si>
+    <t>強度校正</t>
+  </si>
+  <si>
+    <t>邊緣偵測</t>
+  </si>
+  <si>
+    <t>作者建議使用雙重for迴圈的主要原因為何?</t>
+  </si>
+  <si>
+    <t>更直觀、更底層、可轉換為向量法加速</t>
+  </si>
+  <si>
+    <t>cvtColor函數使用數字而非字串代表顏色空間轉換,這樣設計的可能優點是?</t>
+  </si>
+  <si>
+    <t>更容易記憶</t>
+  </si>
+  <si>
+    <t>更容易除錯</t>
+  </si>
+  <si>
+    <t>處理速度更快且更節省記憶體</t>
+  </si>
+  <si>
+    <t>若要同時調整影像的亮度和對比度,應該如何組合運算?</t>
+  </si>
+  <si>
+    <t>先乘法調整對比,再加法調整亮度</t>
+  </si>
+  <si>
+    <t>只用加法</t>
+  </si>
+  <si>
+    <t>只用乘法</t>
+  </si>
+  <si>
+    <t>先減法再除法</t>
+  </si>
+  <si>
+    <t>Mat類別除了儲存像素資訊外,還儲存哪些資訊?</t>
+  </si>
+  <si>
+    <t>相關的影像資訊(如尺寸、類型等)</t>
+  </si>
+  <si>
+    <t>文字註解</t>
+  </si>
+  <si>
+    <t>使用雙重迴圈能寫得更底層,這代表什麼優勢?</t>
+  </si>
+  <si>
+    <t>程式碼更簡單</t>
+  </si>
+  <si>
+    <t>執行速度一定更快</t>
+  </si>
+  <si>
+    <t>能有更多的變換和控制</t>
+  </si>
+  <si>
+    <t>不需要優化</t>
+  </si>
+  <si>
+    <t>從雙重迴圈轉換為向量法的最佳時機是?</t>
+  </si>
+  <si>
+    <t>一開始就使用向量法</t>
+  </si>
+  <si>
+    <t>永遠不轉換</t>
+  </si>
+  <si>
+    <t>隨機選擇</t>
+  </si>
+  <si>
+    <t>完成各類型的數學組合後再轉換</t>
+  </si>
+  <si>
+    <t>查閱OpenCV官方文件時,為什麼需要選擇對應的OpenCV版本?</t>
+  </si>
+  <si>
+    <t>不同版本的函數和功能可能有差異</t>
+  </si>
+  <si>
+    <t>只是習慣</t>
+  </si>
+  <si>
+    <t>網站要求</t>
+  </si>
+  <si>
+    <t>沒有必要</t>
+  </si>
+  <si>
+    <t>影像處理中的基本運算(加減乘除)與數學運算的主要差異在於?</t>
+  </si>
+  <si>
+    <t>完全相同</t>
+  </si>
+  <si>
+    <t>需要考慮像素值範圍限制和溢位問題</t>
+  </si>
+  <si>
+    <t>只能用整數</t>
+  </si>
+  <si>
+    <t>不能使用除法</t>
+  </si>
+  <si>
+    <t>CH 03-影像之Matlab</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -918,19 +1107,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="74.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.75" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>174</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>175</v>
+        <v>8</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>176</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
@@ -955,59 +1152,59 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -1015,79 +1212,79 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F9">
         <v>3</v>
@@ -1095,99 +1292,99 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="F14">
         <v>4</v>
@@ -1195,19 +1392,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1215,19 +1412,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="F16">
         <v>2</v>
@@ -1235,19 +1432,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="E17" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="F17">
         <v>3</v>
@@ -1255,39 +1452,39 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="E18" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -1295,39 +1492,39 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="E21" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="F21">
         <v>3</v>
@@ -1335,79 +1532,79 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="E22" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="E23" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="C24" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="E24" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="D25" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="E25" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="F25">
         <v>3</v>
@@ -1415,19 +1612,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="E26" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="F26">
         <v>4</v>
@@ -1435,19 +1632,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="B27" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="E27" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -1455,19 +1652,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="F28">
         <v>2</v>
@@ -1475,219 +1672,219 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>140</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="E29" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="D30" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="E30" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="B31" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="C31" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="D31" t="s">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="E31" t="s">
-        <v>108</v>
+        <v>12</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="B32" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="C32" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="D32" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="E32" t="s">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>156</v>
       </c>
       <c r="C33" t="s">
-        <v>117</v>
+        <v>157</v>
       </c>
       <c r="D33" t="s">
-        <v>118</v>
+        <v>158</v>
       </c>
       <c r="E33" t="s">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="B34" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="D34" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="E34" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="B35" t="s">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="D35" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="E35" t="s">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="B36" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="C36" t="s">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="D36" t="s">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="E36" t="s">
-        <v>126</v>
+        <v>170</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="B37" t="s">
-        <v>126</v>
+        <v>172</v>
       </c>
       <c r="C37" t="s">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="D37" t="s">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="E37" t="s">
-        <v>127</v>
+        <v>174</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="B38" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="C38" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="D38" t="s">
-        <v>127</v>
+        <v>177</v>
       </c>
       <c r="E38" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="B39" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="C39" t="s">
-        <v>127</v>
+        <v>180</v>
       </c>
       <c r="D39" t="s">
-        <v>126</v>
+        <v>181</v>
       </c>
       <c r="E39" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -1695,39 +1892,39 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>134</v>
+        <v>182</v>
       </c>
       <c r="B40" t="s">
-        <v>68</v>
+        <v>183</v>
       </c>
       <c r="C40" t="s">
-        <v>70</v>
+        <v>184</v>
       </c>
       <c r="D40" t="s">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="E40" t="s">
-        <v>71</v>
+        <v>186</v>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>188</v>
       </c>
       <c r="C41" t="s">
-        <v>137</v>
+        <v>189</v>
       </c>
       <c r="D41" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="E41" t="s">
-        <v>139</v>
+        <v>191</v>
       </c>
       <c r="F41">
         <v>3</v>
@@ -1735,59 +1932,59 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="B42" t="s">
-        <v>87</v>
+        <v>193</v>
       </c>
       <c r="C42" t="s">
-        <v>86</v>
+        <v>194</v>
       </c>
       <c r="D42" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="E42" t="s">
-        <v>88</v>
+        <v>196</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>142</v>
+        <v>197</v>
       </c>
       <c r="B43" t="s">
-        <v>75</v>
+        <v>198</v>
       </c>
       <c r="C43" t="s">
-        <v>66</v>
+        <v>199</v>
       </c>
       <c r="D43" t="s">
-        <v>74</v>
+        <v>200</v>
       </c>
       <c r="E43" t="s">
-        <v>143</v>
+        <v>201</v>
       </c>
       <c r="F43">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="B44" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="C44" t="s">
-        <v>146</v>
+        <v>203</v>
       </c>
       <c r="D44" t="s">
-        <v>75</v>
+        <v>204</v>
       </c>
       <c r="E44" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="F44">
         <v>2</v>
@@ -1795,59 +1992,59 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>147</v>
+        <v>205</v>
       </c>
       <c r="B45" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C45" t="s">
-        <v>89</v>
+        <v>144</v>
       </c>
       <c r="D45" t="s">
-        <v>88</v>
+        <v>206</v>
       </c>
       <c r="E45" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>150</v>
+        <v>207</v>
       </c>
       <c r="B46" t="s">
-        <v>123</v>
+        <v>208</v>
       </c>
       <c r="C46" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="D46" t="s">
-        <v>152</v>
+        <v>209</v>
       </c>
       <c r="E46" t="s">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>153</v>
+        <v>211</v>
       </c>
       <c r="B47" t="s">
-        <v>154</v>
+        <v>212</v>
       </c>
       <c r="C47" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="D47" t="s">
-        <v>156</v>
+        <v>214</v>
       </c>
       <c r="E47" t="s">
-        <v>157</v>
+        <v>215</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -1855,19 +2052,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>158</v>
+        <v>216</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>159</v>
+        <v>217</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="E48" t="s">
-        <v>63</v>
+        <v>218</v>
       </c>
       <c r="F48">
         <v>2</v>
@@ -1875,59 +2072,59 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>160</v>
+        <v>219</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>220</v>
       </c>
       <c r="C49" t="s">
-        <v>46</v>
+        <v>221</v>
       </c>
       <c r="D49" t="s">
-        <v>161</v>
+        <v>222</v>
       </c>
       <c r="E49" t="s">
-        <v>162</v>
+        <v>223</v>
       </c>
       <c r="F49">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>163</v>
+        <v>224</v>
       </c>
       <c r="B50" t="s">
-        <v>46</v>
+        <v>225</v>
       </c>
       <c r="C50" t="s">
-        <v>164</v>
+        <v>226</v>
       </c>
       <c r="D50" t="s">
-        <v>63</v>
+        <v>227</v>
       </c>
       <c r="E50" t="s">
-        <v>48</v>
+        <v>228</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>165</v>
+        <v>229</v>
       </c>
       <c r="B51" t="s">
-        <v>166</v>
+        <v>230</v>
       </c>
       <c r="C51" t="s">
-        <v>167</v>
+        <v>231</v>
       </c>
       <c r="D51" t="s">
-        <v>168</v>
+        <v>232</v>
       </c>
       <c r="E51" t="s">
-        <v>169</v>
+        <v>233</v>
       </c>
       <c r="F51">
         <v>1</v>
@@ -1935,22 +2132,22 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>170</v>
+        <v>234</v>
       </c>
       <c r="B52" t="s">
-        <v>171</v>
+        <v>235</v>
       </c>
       <c r="C52" t="s">
-        <v>33</v>
+        <v>236</v>
       </c>
       <c r="D52" t="s">
-        <v>167</v>
+        <v>237</v>
       </c>
       <c r="E52" t="s">
-        <v>172</v>
+        <v>238</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
